--- a/artfynd/A 1150-2025 artfynd.xlsx
+++ b/artfynd/A 1150-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122448265</v>
+        <v>122442278</v>
       </c>
       <c r="B2" t="n">
-        <v>91194</v>
+        <v>92112</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,17 +714,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långkärret 500m SV, Srm</t>
+          <t>Tallsätter, Tallsätter, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586562</v>
+        <v>586509</v>
       </c>
       <c r="R2" t="n">
-        <v>6548597</v>
+        <v>6548593</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,9 +751,19 @@
           <t>2025-02-03</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,30 +775,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122442278</v>
+        <v>122448265</v>
       </c>
       <c r="B3" t="n">
-        <v>92100</v>
+        <v>91206</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +802,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,17 +829,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tallsätter, Tallsätter, Srm</t>
+          <t>Långkärret 500m SV, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586509</v>
+        <v>586562</v>
       </c>
       <c r="R3" t="n">
-        <v>6548593</v>
+        <v>6548597</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,19 +866,9 @@
           <t>2025-02-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,15 +880,20 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 1150-2025 artfynd.xlsx
+++ b/artfynd/A 1150-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122442278</v>
       </c>
       <c r="B2" t="n">
-        <v>92112</v>
+        <v>92117</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>122448265</v>
       </c>
       <c r="B3" t="n">
-        <v>91206</v>
+        <v>91211</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 1150-2025 artfynd.xlsx
+++ b/artfynd/A 1150-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122442278</v>
+        <v>122448265</v>
       </c>
       <c r="B2" t="n">
-        <v>92117</v>
+        <v>91216</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
+        <v>5420</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,17 +709,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tallsätter, Tallsätter, Srm</t>
+          <t>Långkärret 500m SV, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586509</v>
+        <v>586562</v>
       </c>
       <c r="R2" t="n">
-        <v>6548593</v>
+        <v>6548597</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,19 +746,9 @@
           <t>2025-02-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,25 +760,30 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122448265</v>
+        <v>122442278</v>
       </c>
       <c r="B3" t="n">
-        <v>91211</v>
+        <v>92122</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,25 +792,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Grovticka</t>
-        </is>
+        <v>5966</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,17 +814,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långkärret 500m SV, Srm</t>
+          <t>Tallsätter, Tallsätter, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586562</v>
+        <v>586509</v>
       </c>
       <c r="R3" t="n">
-        <v>6548597</v>
+        <v>6548593</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,9 +851,19 @@
           <t>2025-02-03</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,20 +875,15 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 1150-2025 artfynd.xlsx
+++ b/artfynd/A 1150-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122448265</v>
+        <v>122442278</v>
       </c>
       <c r="B2" t="n">
-        <v>91216</v>
+        <v>92135</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>5966</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -709,17 +714,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långkärret 500m SV, Srm</t>
+          <t>Tallsätter, Tallsätter, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586562</v>
+        <v>586509</v>
       </c>
       <c r="R2" t="n">
-        <v>6548597</v>
+        <v>6548593</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,9 +751,19 @@
           <t>2025-02-03</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,30 +775,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122442278</v>
+        <v>122448265</v>
       </c>
       <c r="B3" t="n">
-        <v>92122</v>
+        <v>91229</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -792,20 +802,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>5420</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -814,17 +829,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tallsätter, Tallsätter, Srm</t>
+          <t>Långkärret 500m SV, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586509</v>
+        <v>586562</v>
       </c>
       <c r="R3" t="n">
-        <v>6548593</v>
+        <v>6548597</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,19 +866,9 @@
           <t>2025-02-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,15 +880,20 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 1150-2025 artfynd.xlsx
+++ b/artfynd/A 1150-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122442278</v>
       </c>
       <c r="B2" t="n">
-        <v>92135</v>
+        <v>92148</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>122448265</v>
       </c>
       <c r="B3" t="n">
-        <v>91229</v>
+        <v>91242</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 1150-2025 artfynd.xlsx
+++ b/artfynd/A 1150-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122442278</v>
+        <v>122448265</v>
       </c>
       <c r="B2" t="n">
-        <v>92148</v>
+        <v>91243</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,17 +714,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tallsätter, Tallsätter, Srm</t>
+          <t>Långkärret 500m SV, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586509</v>
+        <v>586562</v>
       </c>
       <c r="R2" t="n">
-        <v>6548593</v>
+        <v>6548597</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,19 +751,9 @@
           <t>2025-02-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,25 +765,30 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122448265</v>
+        <v>122442278</v>
       </c>
       <c r="B3" t="n">
-        <v>91242</v>
+        <v>92149</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,25 +797,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,17 +824,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långkärret 500m SV, Srm</t>
+          <t>Tallsätter, Tallsätter, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586562</v>
+        <v>586509</v>
       </c>
       <c r="R3" t="n">
-        <v>6548597</v>
+        <v>6548593</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,9 +861,19 @@
           <t>2025-02-03</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,20 +885,15 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 1150-2025 artfynd.xlsx
+++ b/artfynd/A 1150-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122448265</v>
+        <v>122442278</v>
       </c>
       <c r="B2" t="n">
-        <v>91243</v>
+        <v>92149</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,17 +714,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långkärret 500m SV, Srm</t>
+          <t>Tallsätter, Tallsätter, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586562</v>
+        <v>586509</v>
       </c>
       <c r="R2" t="n">
-        <v>6548597</v>
+        <v>6548593</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,9 +751,19 @@
           <t>2025-02-03</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,30 +775,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122442278</v>
+        <v>122448265</v>
       </c>
       <c r="B3" t="n">
-        <v>92149</v>
+        <v>91243</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +802,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,17 +829,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tallsätter, Tallsätter, Srm</t>
+          <t>Långkärret 500m SV, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586509</v>
+        <v>586562</v>
       </c>
       <c r="R3" t="n">
-        <v>6548593</v>
+        <v>6548597</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,19 +866,9 @@
           <t>2025-02-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,15 +880,20 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 1150-2025 artfynd.xlsx
+++ b/artfynd/A 1150-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122442278</v>
+        <v>122448265</v>
       </c>
       <c r="B2" t="n">
-        <v>92256</v>
+        <v>91354</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,17 +714,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tallsätter, Tallsätter, Srm</t>
+          <t>Långkärret 500m SV, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586509</v>
+        <v>586562</v>
       </c>
       <c r="R2" t="n">
-        <v>6548593</v>
+        <v>6548597</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,19 +751,9 @@
           <t>2025-02-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,25 +765,30 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122448265</v>
+        <v>122442278</v>
       </c>
       <c r="B3" t="n">
-        <v>91350</v>
+        <v>92260</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,25 +797,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,17 +824,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långkärret 500m SV, Srm</t>
+          <t>Tallsätter, Tallsätter, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586562</v>
+        <v>586509</v>
       </c>
       <c r="R3" t="n">
-        <v>6548597</v>
+        <v>6548593</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,9 +861,19 @@
           <t>2025-02-03</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,20 +885,15 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 1150-2025 artfynd.xlsx
+++ b/artfynd/A 1150-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>122448265</v>
       </c>
       <c r="B2" t="n">
-        <v>91354</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,12 +783,7 @@
         <v>122442278</v>
       </c>
       <c r="B3" t="n">
-        <v>92260</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1150-2025 artfynd.xlsx
+++ b/artfynd/A 1150-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122448265</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,8 +897,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122442278</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>